--- a/Config_по_электростанциям.xlsx
+++ b/Config_по_электростанциям.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -438,8 +438,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,10 +532,20 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>Источник_параметров</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -595,8 +607,12 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -658,8 +674,12 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -721,8 +741,12 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -784,8 +808,12 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -847,8 +875,12 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -910,8 +942,16 @@
       <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
       <c r="S7" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -973,8 +1013,16 @@
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1036,8 +1084,16 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1099,8 +1155,16 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
       <c r="S10" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1162,8 +1226,16 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
       <c r="S11" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1225,8 +1297,16 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
       <c r="S12" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1288,8 +1368,16 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
       <c r="S13" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1351,8 +1439,16 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
       <c r="S14" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -1418,12 +1514,16 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1489,12 +1589,16 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1560,12 +1664,16 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1631,12 +1739,16 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1702,12 +1814,16 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1773,12 +1889,16 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1844,12 +1964,16 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -1866,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1886,9 +2010,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="31" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1977,7 +2102,17 @@
           <t>В сумму станции (1/0)</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
       <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>Глобальные настройки</t>
         </is>
@@ -2039,12 +2174,16 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>fном, Гц</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2104,12 +2243,16 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>Время начала события</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2167,12 +2310,16 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Автопоиск старта (1/0)</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2232,12 +2379,16 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Колич. интервал, с</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>82</v>
       </c>
     </row>
@@ -2297,12 +2448,16 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Допуск количеств., %</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2362,12 +2517,20 @@
       <c r="Q7" t="n">
         <v>1</v>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>Порог включения в работу, МВт</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2427,6 +2590,22 @@
       <c r="Q8" t="n">
         <v>1</v>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Pre-start буфер, с</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2484,6 +2663,22 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Интервал графика, с</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2541,6 +2736,14 @@
       <c r="Q10" t="n">
         <v>1</v>
       </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2598,6 +2801,14 @@
       <c r="Q11" t="n">
         <v>1</v>
       </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2655,6 +2866,14 @@
       <c r="Q12" t="n">
         <v>1</v>
       </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2712,6 +2931,14 @@
       <c r="Q13" t="n">
         <v>1</v>
       </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2769,6 +2996,14 @@
       <c r="Q14" t="n">
         <v>1</v>
       </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2830,6 +3065,10 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2891,6 +3130,10 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2952,6 +3195,10 @@
       <c r="Q17" t="n">
         <v>0</v>
       </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3013,6 +3260,10 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3074,6 +3325,10 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3135,6 +3390,10 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3196,6 +3455,10 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3208,7 +3471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3228,8 +3491,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="48" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="48" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3320,10 +3585,20 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>Источник_параметров</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -3385,8 +3660,12 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -3448,8 +3727,12 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -3511,8 +3794,12 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -3574,8 +3861,12 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -3637,8 +3928,12 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Осциллограммы - Печорская ГРЭС 28.01.2026.xlsx</t>
         </is>
@@ -3655,7 +3950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3675,8 +3970,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="38" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3767,10 +4064,20 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>Источник_параметров</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -3832,8 +4139,16 @@
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
       <c r="S2" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -3895,8 +4210,16 @@
       <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
       <c r="S3" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -3958,8 +4281,16 @@
       <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
       <c r="S4" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4021,8 +4352,16 @@
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
       <c r="S5" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4084,8 +4423,16 @@
       <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
       <c r="S6" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4147,8 +4494,16 @@
       <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
       <c r="S7" t="inlineStr">
+        <is>
+          <t>Э</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4210,8 +4565,16 @@
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
       <c r="S8" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4273,8 +4636,16 @@
       <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
       <c r="S9" t="inlineStr">
+        <is>
+          <t>У</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>Осциллограммы - СЛПК 28.01.2026.xlsx</t>
         </is>
@@ -4291,7 +4662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4311,8 +4682,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="47" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="47" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4403,10 +4776,20 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>Источник_параметров</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -4472,12 +4855,16 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -4543,12 +4930,16 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -4614,12 +5005,16 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -4685,12 +5080,16 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Осциллограммы - Усинской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -4707,7 +5106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4727,8 +5126,10 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="47" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
+    <col width="47" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4819,10 +5220,20 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>Контр_уст (1/0)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Паропровод</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>Источник_параметров</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Файл</t>
         </is>
@@ -4888,12 +5299,16 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -4959,12 +5374,16 @@
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
@@ -5030,12 +5449,16 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>oik_embedded</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Осциллограммы - Ярегской ТЭЦ 28.01.2026.xlsx</t>
         </is>
